--- a/PinAssignment/Rev_D_Pin_assignment.xlsx
+++ b/PinAssignment/Rev_D_Pin_assignment.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gaurav\Documents\FMC_Camera_MIPI_Breakout_Board\PinAssignment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8199A5D-9584-4523-B2B4-596F76F6B9CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6399D846-1018-4658-8350-84E68546AEFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{769B0726-CEFB-470C-B5E0-AD07EF98B319}"/>
+    <workbookView xWindow="30612" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{769B0726-CEFB-470C-B5E0-AD07EF98B319}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -270,12 +270,6 @@
     <t>AH1</t>
   </si>
   <si>
-    <t>H18</t>
-  </si>
-  <si>
-    <t>H17</t>
-  </si>
-  <si>
     <t>G10</t>
   </si>
   <si>
@@ -529,6 +523,12 @@
   </si>
   <si>
     <t xml:space="preserve">F8 </t>
+  </si>
+  <si>
+    <t>K17</t>
+  </si>
+  <si>
+    <t>J17</t>
   </si>
 </sst>
 </file>
@@ -616,13 +616,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -946,10 +946,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
@@ -964,13 +964,13 @@
       <c r="F1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="5" t="s">
-        <v>149</v>
+      <c r="G1" s="3" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="4"/>
-      <c r="B2" s="4"/>
+      <c r="A2" s="5"/>
+      <c r="B2" s="5"/>
       <c r="C2" s="2" t="s">
         <v>3</v>
       </c>
@@ -983,7 +983,7 @@
       <c r="F2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="3" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1004,10 +1004,10 @@
         <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="G3" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -1027,10 +1027,10 @@
         <v>14</v>
       </c>
       <c r="F4" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="G4" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -1050,10 +1050,10 @@
         <v>17</v>
       </c>
       <c r="F5" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="G5" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -1073,10 +1073,10 @@
         <v>20</v>
       </c>
       <c r="F6" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="G6" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
@@ -1096,10 +1096,10 @@
         <v>23</v>
       </c>
       <c r="F7" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="G7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
@@ -1110,19 +1110,19 @@
         <v>24</v>
       </c>
       <c r="C8" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D8" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E8" t="s">
-        <v>81</v>
+        <v>166</v>
       </c>
       <c r="F8" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G8" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
@@ -1136,16 +1136,16 @@
         <v>74</v>
       </c>
       <c r="D9" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E9" t="s">
-        <v>82</v>
+        <v>167</v>
       </c>
       <c r="F9" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="G9" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
@@ -1156,19 +1156,19 @@
         <v>28</v>
       </c>
       <c r="C10" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D10" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E10" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F10" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="G10" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
@@ -1179,19 +1179,19 @@
         <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D11" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E11" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F11" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="G11" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
@@ -1207,16 +1207,16 @@
         <v>20</v>
       </c>
       <c r="C14" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D14" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E14" t="s">
         <v>33</v>
       </c>
       <c r="F14" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="G14" t="s">
         <v>33</v>
@@ -1233,7 +1233,7 @@
         <v>36</v>
       </c>
       <c r="F15" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="G15" t="s">
         <v>34</v>
@@ -1250,7 +1250,7 @@
         <v>39</v>
       </c>
       <c r="F16" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G16" t="s">
         <v>39</v>
@@ -1264,13 +1264,13 @@
         <v>40</v>
       </c>
       <c r="E17" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F17" t="s">
         <v>48</v>
       </c>
       <c r="G17" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
@@ -1281,13 +1281,13 @@
         <v>36</v>
       </c>
       <c r="E18" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F18" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="G18" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
@@ -1298,13 +1298,13 @@
         <v>43</v>
       </c>
       <c r="E19" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F19" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="G19" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
@@ -1315,13 +1315,13 @@
         <v>45</v>
       </c>
       <c r="E20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F20" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="G20" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
@@ -1337,16 +1337,16 @@
         <v>48</v>
       </c>
       <c r="C23" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D23" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E23" t="s">
         <v>24</v>
       </c>
       <c r="F23" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="G23" t="s">
         <v>24</v>
@@ -1360,13 +1360,13 @@
         <v>50</v>
       </c>
       <c r="C24" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E24" t="s">
         <v>52</v>
       </c>
       <c r="G24" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
@@ -1377,13 +1377,13 @@
         <v>53</v>
       </c>
       <c r="C25" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E25" t="s">
         <v>55</v>
       </c>
       <c r="G25" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
@@ -1394,13 +1394,13 @@
         <v>56</v>
       </c>
       <c r="C26" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E26" t="s">
         <v>58</v>
       </c>
       <c r="G26" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
@@ -1411,7 +1411,7 @@
         <v>59</v>
       </c>
       <c r="C27" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E27" t="s">
         <v>61</v>
@@ -1428,13 +1428,13 @@
         <v>62</v>
       </c>
       <c r="C28" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E28" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G28" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
@@ -1445,13 +1445,13 @@
         <v>64</v>
       </c>
       <c r="C29" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E29" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G29" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
@@ -1462,13 +1462,13 @@
         <v>66</v>
       </c>
       <c r="C30" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E30" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G30" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
@@ -1479,123 +1479,123 @@
         <v>68</v>
       </c>
       <c r="C31" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E31" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="G31" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B35" t="s">
+        <v>101</v>
+      </c>
+      <c r="C35" t="s">
         <v>103</v>
       </c>
-      <c r="C35" t="s">
-        <v>105</v>
-      </c>
       <c r="D35" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E35" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B36" t="s">
+        <v>104</v>
+      </c>
+      <c r="C36" t="s">
         <v>106</v>
-      </c>
-      <c r="C36" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B37" t="s">
+        <v>107</v>
+      </c>
+      <c r="C37" t="s">
         <v>109</v>
-      </c>
-      <c r="C37" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B38" t="s">
+        <v>110</v>
+      </c>
+      <c r="C38" t="s">
         <v>112</v>
-      </c>
-      <c r="C38" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B39" t="s">
+        <v>113</v>
+      </c>
+      <c r="C39" t="s">
         <v>115</v>
-      </c>
-      <c r="C39" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B40" t="s">
+        <v>116</v>
+      </c>
+      <c r="C40" t="s">
         <v>118</v>
-      </c>
-      <c r="C40" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B41" t="s">
+        <v>119</v>
+      </c>
+      <c r="C41" t="s">
         <v>121</v>
-      </c>
-      <c r="C41" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B42" t="s">
+        <v>122</v>
+      </c>
+      <c r="C42" t="s">
         <v>124</v>
-      </c>
-      <c r="C42" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B43" t="s">
+        <v>125</v>
+      </c>
+      <c r="C43" t="s">
         <v>127</v>
-      </c>
-      <c r="C43" t="s">
-        <v>129</v>
       </c>
     </row>
   </sheetData>
